--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>For Hire</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>For Hire - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G2" t="str">
-        <v>3:44</v>
+        <v>2:30</v>
       </c>
       <c r="H2" t="str">
-        <v>People I’ve Met</v>
+        <v>Thundercat</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L2" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>For Hire</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Don't Be Dumb</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>2:20</v>
+        <v>3:44</v>
       </c>
       <c r="H5" t="str">
-        <v>A$AP Rocky</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L5" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CAMBIARÉ</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v>2:20</v>
       </c>
       <c r="H6" t="str">
-        <v>Luis Fonsi</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L6" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Piss In The Wind</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>2:29</v>
+        <v>3:01</v>
       </c>
       <c r="H7" t="str">
-        <v>Joji</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L7" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>High Key</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Vacancy</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G8" t="str">
-        <v>2:12</v>
+        <v>2:29</v>
       </c>
       <c r="H8" t="str">
-        <v>Ari Lennox</v>
+        <v>Joji</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L8" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>scared</v>
+        <v>High Key</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>scared - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G9" t="str">
-        <v>3:46</v>
+        <v>2:12</v>
       </c>
       <c r="H9" t="str">
-        <v>Fred again..</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L9" t="str">
-        <v>scared - Fred again..</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Death of Love</v>
+        <v>scared</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Trying Times</v>
+        <v>scared - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H10" t="str">
-        <v>James Blake</v>
+        <v>Fred again..</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L10" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Death of Love</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G11" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H11" t="str">
-        <v>Parker McCollum</v>
+        <v>James Blake</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L11" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ATM</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>OCTANE</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G12" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H12" t="str">
-        <v>Don Toliver</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L12" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Flo Jackson</v>
+        <v>ATM</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G13" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H13" t="str">
-        <v>Flo Milli</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L13" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H14" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L14" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G15" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H15" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L15" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G16" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H16" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L16" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G17" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H17" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L17" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H18" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L18" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G19" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L19" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G20" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H20" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L20" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H21" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L21" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G22" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H22" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L22" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H23" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L23" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Losing You</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G24" t="str">
-        <v>3:02</v>
+        <v>2:22</v>
       </c>
       <c r="H24" t="str">
-        <v>The Runarounds</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L24" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Infinito</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H25" t="str">
-        <v>Yandel</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L25" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G26" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L26" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G27" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H27" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L27" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G28" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H28" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L28" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G29" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L29" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H30" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L30" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G31" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L31" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G32" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L32" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G33" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L33" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H34" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L34" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H35" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L35" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H36" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L36" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G37" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H37" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L37" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G38" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H38" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L38" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G39" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H39" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L39" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G40" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H40" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L40" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H41" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L41" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G42" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H42" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L42" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H43" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L43" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H44" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L44" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H45" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L45" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>dust to dust</v>
+        <v>Funeral</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G46" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H46" t="str">
-        <v>Truman Sinclair</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L46" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H47" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L47" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H48" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L48" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G49" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H49" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L49" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L50" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H51" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L51" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H52" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L52" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H53" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L53" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H54" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L54" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G55" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H55" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L55" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H56" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L56" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G57" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H57" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L57" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H58" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L58" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G59" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H59" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L59" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L60" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H61" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L61" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H62" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L62" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H63" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L63" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G64" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H64" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L64" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H65" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L65" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G66" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L66" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G67" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H67" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L67" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H68" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L68" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H69" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L69" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H70" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L70" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H71" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L71" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H72" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L72" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H73" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L73" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G74" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H74" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L74" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H75" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L75" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H76" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L76" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L77" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H78" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L78" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G79" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H79" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L79" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G80" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H80" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L80" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G81" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H81" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L81" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H82" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L82" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G83" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H83" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L83" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H84" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L84" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H85" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L85" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G86" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H86" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L86" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H87" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L87" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H88" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L88" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H89" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L89" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G90" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H90" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L90" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H91" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L91" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H92" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L92" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G93" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H93" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L93" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3947,68 +3947,106 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G94" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H94" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L94" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G95" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K95" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D95" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
+      <c r="D96" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G96" t="str">
         <v>2:41</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H96" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K96" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L95" t="str">
+      <c r="L96" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E96" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>I Did This To Myself</v>
+        <v>Body</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Distracted</v>
+        <v>OCTANE</v>
       </c>
       <c r="G2" t="str">
-        <v>2:30</v>
+        <v>2:35</v>
       </c>
       <c r="H2" t="str">
-        <v>Thundercat</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L2" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Aperture</v>
+        <v>Dandelion</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-30</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Dandelion</v>
       </c>
       <c r="G3" t="str">
-        <v>5:11</v>
+        <v>4:00</v>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L3" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Opening Night</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-30</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>HELP(2)</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>4:19</v>
+        <v>2:38</v>
       </c>
       <c r="H4" t="str">
-        <v>Arctic Monkeys</v>
+        <v>John Summit</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L4" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>For Hire</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-30</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>For Hire - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G5" t="str">
-        <v>3:44</v>
+        <v>5:17</v>
       </c>
       <c r="H5" t="str">
-        <v>People I’ve Met</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L5" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>triston</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/triston/1872585947</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-30</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Don't Be Dumb</v>
+        <v>triston - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>2:20</v>
+        <v>3:36</v>
       </c>
       <c r="H6" t="str">
-        <v>A$AP Rocky</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/triston/1872585761</v>
       </c>
       <c r="L6" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>triston - Fuerza Regida</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-30</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H7" t="str">
-        <v>Luis Fonsi</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L7" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-30</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Piss In The Wind</v>
+        <v>Distracted</v>
       </c>
       <c r="G8" t="str">
-        <v>2:29</v>
+        <v>2:30</v>
       </c>
       <c r="H8" t="str">
-        <v>Joji</v>
+        <v>Thundercat</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L8" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>High Key</v>
+        <v>For Hire</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-30</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Vacancy</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>2:12</v>
+        <v>3:44</v>
       </c>
       <c r="H9" t="str">
-        <v>Ari Lennox</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L9" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>scared</v>
+        <v>McArthur</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-30</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>scared - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:46</v>
+        <v>3:51</v>
       </c>
       <c r="H10" t="str">
-        <v>Fred again..</v>
+        <v>HARDY</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L10" t="str">
-        <v>scared - Fred again..</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Death of Love</v>
+        <v>Debris</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-30</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Trying Times</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G11" t="str">
-        <v>3:26</v>
+        <v>2:55</v>
       </c>
       <c r="H11" t="str">
-        <v>James Blake</v>
+        <v>Labrinth</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L11" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-30</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>4:03</v>
+        <v>4:38</v>
       </c>
       <c r="H12" t="str">
-        <v>Parker McCollum</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L12" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ATM</v>
+        <v>1+1</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-30</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>OCTANE</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:00</v>
+        <v>3:06</v>
       </c>
       <c r="H13" t="str">
-        <v>Don Toliver</v>
+        <v>Maluma</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L13" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Flo Jackson</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-30</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:23</v>
+        <v>3:08</v>
       </c>
       <c r="H14" t="str">
-        <v>Flo Milli</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L14" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>fml .</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-30</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Creature of Habit</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v>2:40</v>
       </c>
       <c r="H15" t="str">
-        <v>Courtney Barnett</v>
+        <v>fakemink</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L15" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Puppet Parade</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-30</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Megadeth</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>4:40</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Megadeth</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L16" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>To Love Somebody</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-30</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Cruel World</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H17" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L17" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>Lorelei</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-30</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>4:14</v>
+        <v>2:35</v>
       </c>
       <c r="H18" t="str">
-        <v>Cleo Sol</v>
+        <v>ERNEST</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L18" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Free</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-30</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>THE CORE - 核</v>
+        <v>Free - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:56</v>
       </c>
       <c r="H19" t="str">
-        <v>XG</v>
+        <v>SLANDER</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L19" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Dead End</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-30</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Ricochet</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>4:05</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Snail Mail</v>
+        <v>Artemas</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L20" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-30</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G21" t="str">
-        <v>3:52</v>
+        <v>3:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Dove Cameron</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L21" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Aguas</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-30</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:02</v>
+        <v>2:52</v>
       </c>
       <c r="H22" t="str">
-        <v>Kenia Os</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L22" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BAD</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-30</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BAD - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:15</v>
+        <v>2:48</v>
       </c>
       <c r="H23" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L23" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Losing You</v>
+        <v>Baddie</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-30</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>F.I.G</v>
+        <v>Bohemio</v>
       </c>
       <c r="G24" t="str">
-        <v>2:22</v>
+        <v>3:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Naomi Scott</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L24" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-30</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:02</v>
+        <v>3:51</v>
       </c>
       <c r="H25" t="str">
-        <v>The Runarounds</v>
+        <v>Tems</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L25" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-30</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Infinito</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:14</v>
+        <v>3:16</v>
       </c>
       <c r="H26" t="str">
-        <v>Yandel</v>
+        <v>Fred again..</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L26" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Sexy For Me</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-30</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:08</v>
+        <v>3:50</v>
       </c>
       <c r="H27" t="str">
-        <v>Jason Derulo</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L27" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Turbulence</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-30</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G28" t="str">
-        <v>2:25</v>
+        <v>3:33</v>
       </c>
       <c r="H28" t="str">
-        <v>Wizkid</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L28" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-30</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>3:17</v>
       </c>
       <c r="H29" t="str">
-        <v>Jelly Roll</v>
+        <v>Kneecap</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L29" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-30</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:47</v>
+        <v>4:38</v>
       </c>
       <c r="H30" t="str">
-        <v>Dolly Parton</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-30</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:53</v>
+        <v>3:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L31" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>HIGH</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-30</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Act I</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G32" t="str">
-        <v>3:43</v>
+        <v>3:23</v>
       </c>
       <c r="H32" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L32" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Imposter</v>
+        <v>Villain</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-30</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Reflections</v>
       </c>
       <c r="G33" t="str">
-        <v>2:38</v>
+        <v>3:53</v>
       </c>
       <c r="H33" t="str">
-        <v>Louis Tomlinson</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L33" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-30</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G34" t="str">
-        <v>6:01</v>
+        <v>3:00</v>
       </c>
       <c r="H34" t="str">
-        <v>Not for Radio</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L34" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Residue</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-30</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G35" t="str">
-        <v>2:24</v>
+        <v>3:28</v>
       </c>
       <c r="H35" t="str">
-        <v>GIRLSET</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L35" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>I Could Get Used To This</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-30</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G36" t="str">
-        <v>3:41</v>
+        <v>2:12</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie Ware</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L36" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LA VILLA</v>
+        <v>Starlight</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-30</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G37" t="str">
-        <v>3:12</v>
+        <v>3:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Ryan Castro</v>
+        <v>Cannons</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L37" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Dandelion</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-30</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G38" t="str">
-        <v>3:27</v>
+        <v>3:14</v>
       </c>
       <c r="H38" t="str">
-        <v>Denzel Curry</v>
+        <v>Dogpark</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L38" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Thick One</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-30</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Part 3</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G39" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H39" t="str">
-        <v>42 Dugg</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L39" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-30</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G40" t="str">
-        <v>3:59</v>
+        <v>2:24</v>
       </c>
       <c r="H40" t="str">
-        <v>Lucinda Williams</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L40" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>THUM</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-30</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>THUM - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G41" t="str">
-        <v>2:11</v>
+        <v>1:59</v>
       </c>
       <c r="H41" t="str">
-        <v>Violet Grohl</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L41" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-30</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>The Great Satan</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:32</v>
+        <v>3:02</v>
       </c>
       <c r="H42" t="str">
-        <v>Rob Zombie</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L42" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Excuses For Love</v>
+        <v>Prettier</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-30</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Hyperlove</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:04</v>
+        <v>2:34</v>
       </c>
       <c r="H43" t="str">
-        <v>MIKA</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L43" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>3 Tears</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-30</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 Tears - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:50</v>
+        <v>3:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Mergui</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L44" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Church Girl</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-30</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Church Girl - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:19</v>
+        <v>3:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Carly Pearce</v>
+        <v>The Maine</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L45" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Funeral</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-30</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>The Weight of the Woods</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>4:03</v>
+        <v>2:58</v>
       </c>
       <c r="H46" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L46" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>dust to dust</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-30</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G47" t="str">
-        <v>3:51</v>
+        <v>2:14</v>
       </c>
       <c r="H47" t="str">
-        <v>Truman Sinclair</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L47" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Say Yes</v>
+        <v>Too Late</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-30</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Say Yes - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G48" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H48" t="str">
-        <v>Marques Anthony</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L48" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-30</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>CAMPILATION</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Camper</v>
+        <v>i-dle</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L49" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ojalá</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-30</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Ojalá - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>1:55</v>
       </c>
       <c r="H50" t="str">
-        <v>Lunay</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L50" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>RIDIN</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-30</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:17</v>
+        <v>2:00</v>
       </c>
       <c r="H51" t="str">
-        <v>Ledbyher</v>
+        <v>Tokischa</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L51" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Wallflower</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-30</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Wallflower - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:25</v>
+        <v>3:07</v>
       </c>
       <c r="H52" t="str">
-        <v>Sikarus</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L52" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>You Phase</v>
+        <v>Poema</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-30</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>You Phase - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:51</v>
+        <v>3:14</v>
       </c>
       <c r="H53" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L53" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Miss Independent</v>
+        <v>Live Without</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-30</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Miss Independent - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G54" t="str">
-        <v>2:40</v>
+        <v>2:55</v>
       </c>
       <c r="H54" t="str">
-        <v>1Ski OG</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L54" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-30</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>5:47</v>
+        <v>3:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Elevation Worship</v>
+        <v>Blessd</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L55" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>go again</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-30</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>go again - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:07</v>
+        <v>3:31</v>
       </c>
       <c r="H56" t="str">
-        <v>NateTaylorr</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L56" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Autopilot</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-30</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Autopilot</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:46</v>
+        <v>2:45</v>
       </c>
       <c r="H57" t="str">
-        <v>ALEXSUCKS</v>
+        <v>VEDO</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L57" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-30</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H58" t="str">
-        <v>SPELLLING</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L58" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>In Violet</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-30</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G59" t="str">
-        <v>4:09</v>
+        <v>3:20</v>
       </c>
       <c r="H59" t="str">
-        <v>Searows</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L59" t="str">
-        <v>In Violet - Searows</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Baby Run</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-30</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Baby Run - Single</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>4:47</v>
+        <v>2:48</v>
       </c>
       <c r="H60" t="str">
-        <v>Jimi Jules</v>
+        <v>Mýa</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L60" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>What If We Don't</v>
+        <v>Once I Say</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-30</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>What If We Don't - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G61" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>Ashley McBryde</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L61" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Hagamos Que</v>
+        <v>believer</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-30</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H62" t="str">
-        <v>Juanes</v>
+        <v>Yuna</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L62" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>World Change Me</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-30</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>World Change Me - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:03</v>
+        <v>3:51</v>
       </c>
       <c r="H63" t="str">
-        <v>Max McNown</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L63" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Exclusive</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-30</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Exclusive - EP</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G64" t="str">
-        <v>3:20</v>
+        <v>3:13</v>
       </c>
       <c r="H64" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L64" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Say Less</v>
+        <v>Daysa</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-30</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Say Less - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:18</v>
+        <v>4:36</v>
       </c>
       <c r="H65" t="str">
-        <v>JYT</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L65" t="str">
-        <v>Say Less - JYT</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Angels Cry</v>
+        <v>Fabulous</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-30</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:52</v>
+        <v>2:33</v>
       </c>
       <c r="H66" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>MEEK</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L66" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Over You</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-30</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>A Love For Strangers</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:44</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>Chet Faker</v>
+        <v>RUBIO</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L67" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>brainchem</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-30</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:42</v>
+        <v>2:28</v>
       </c>
       <c r="H68" t="str">
-        <v>Barry Can't Swim</v>
+        <v>EMJAY</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L68" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-30</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G69" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H69" t="str">
-        <v>Disco Lines</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L69" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Giants</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-30</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H70" t="str">
-        <v>David Guetta</v>
+        <v>Picture This</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L70" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Rejoice</v>
+        <v>Scooby</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-30</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Rejoice - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>4:20</v>
+        <v>3:41</v>
       </c>
       <c r="H71" t="str">
-        <v>Def Leppard</v>
+        <v>corook</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L71" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>La Racha</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-30</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:58</v>
+        <v>2:48</v>
       </c>
       <c r="H72" t="str">
-        <v>Honey Dijon</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L72" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Odisea</v>
+        <v>So Am I</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-30</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Odisea - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G73" t="str">
-        <v>3:56</v>
+        <v>2:50</v>
       </c>
       <c r="H73" t="str">
-        <v>BASSYY</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L73" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lucky Day</v>
+        <v>best thing</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-30</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Speed Kills</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:13</v>
+        <v>4:27</v>
       </c>
       <c r="H74" t="str">
-        <v>Ally Evenson</v>
+        <v>WRABEL</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L74" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Breathe On It</v>
+        <v>Count It Back</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-30</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G75" t="str">
-        <v>4:00</v>
+        <v>2:52</v>
       </c>
       <c r="H75" t="str">
-        <v>Tauren Wells</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L75" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Easy</v>
+        <v>Good Girl</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-30</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Easy - Single</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:30</v>
+        <v>4:23</v>
       </c>
       <c r="H76" t="str">
-        <v>lydi lynn</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L76" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Break Me In</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-30</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Break Me In - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G77" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H77" t="str">
-        <v>Joyce Wrice</v>
+        <v>MORGXN</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L77" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Long Live Love</v>
+        <v>Run My Way</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-30</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:36</v>
+        <v>2:44</v>
       </c>
       <c r="H78" t="str">
-        <v>Sugar</v>
+        <v>December 10</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L78" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Depressed</v>
+        <v>Cold Night</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-30</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Boycott Heaven</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:32</v>
+        <v>3:12</v>
       </c>
       <c r="H79" t="str">
-        <v>The Format</v>
+        <v>HANA</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L79" t="str">
-        <v>Depressed - The Format</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Empty Hands</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-30</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Empty Hands</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:09</v>
+        <v>2:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Poppy</v>
+        <v>LUNA</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L80" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Long Surrender</v>
+        <v>Fragile</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-30</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>The Long Surrender</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:45</v>
+        <v>3:10</v>
       </c>
       <c r="H81" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Anajah</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L81" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Angela</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-30</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Angela - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:32</v>
+        <v>2:04</v>
       </c>
       <c r="H82" t="str">
-        <v>Hayden Everett</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L82" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Disappear</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-30</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Greyhound</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:31</v>
+        <v>3:04</v>
       </c>
       <c r="H83" t="str">
-        <v>Katie Tupper</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L83" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Catapult</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-30</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Catapult - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:57</v>
+        <v>3:41</v>
       </c>
       <c r="H84" t="str">
-        <v>Cape Francis</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L84" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Think Twice</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-30</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Think Twice - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G85" t="str">
-        <v>2:22</v>
+        <v>3:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Leonie Biney</v>
+        <v>Sevendust</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L85" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LOVESONGS</v>
+        <v>Hud</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-30</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G86" t="str">
-        <v>3:33</v>
+        <v>4:46</v>
       </c>
       <c r="H86" t="str">
-        <v>Agnes</v>
+        <v>MØL</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L86" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Down South</v>
+        <v>Ego Death</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-30</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Down South - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:19</v>
+        <v>2:12</v>
       </c>
       <c r="H87" t="str">
-        <v>Trap Dickey</v>
+        <v>Atreyu</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L87" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-30</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:16</v>
+        <v>4:05</v>
       </c>
       <c r="H88" t="str">
-        <v>SALIMATA</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L88" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Love Like This</v>
+        <v>Disappear</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-30</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Love Like This - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G89" t="str">
-        <v>3:30</v>
+        <v>5:50</v>
       </c>
       <c r="H89" t="str">
-        <v>Jacob Banks</v>
+        <v>Lane 8</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L89" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Plan Plan</v>
+        <v>Misbehave</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-30</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:10</v>
+        <v>3:43</v>
       </c>
       <c r="H90" t="str">
-        <v>Funky</v>
+        <v>Aluna</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L90" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>double edged sword</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-30</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>double edged sword - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:28</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>Hailey Picardi</v>
+        <v>Alok</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L91" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Fly</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-30</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:27</v>
+        <v>3:04</v>
       </c>
       <c r="H92" t="str">
-        <v>Matt Hansen</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L92" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Decay</v>
+        <v>ily anyway</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-30</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:20</v>
+        <v>3:05</v>
       </c>
       <c r="H93" t="str">
-        <v>Pop Evil</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L93" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>3111</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-30</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Goliath</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G94" t="str">
-        <v>4:08</v>
+        <v>3:35</v>
       </c>
       <c r="H94" t="str">
-        <v>Exodus</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L94" t="str">
-        <v>3111 - Exodus</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-30</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G95" t="str">
-        <v>2:57</v>
+        <v>3:41</v>
       </c>
       <c r="H95" t="str">
-        <v>Myrkur</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L95" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bomb To A Knife Fight</v>
+        <v>praxis</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-30</v>
@@ -4023,30 +4023,182 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G96" t="str">
-        <v>2:41</v>
+        <v>3:28</v>
       </c>
       <c r="H96" t="str">
-        <v>The Barbarians of California</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L96" t="str">
-        <v>Bomb To A Knife Fight - The Barbarians of California</v>
+        <v>praxis - Lauren Auder</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>House</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>https://music.apple.com/us/song/house/1866696487</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>House - Single</v>
+      </c>
+      <c r="G97" t="str">
+        <v>2:30</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Connie Converse</v>
+      </c>
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+      </c>
+      <c r="K97" t="str">
+        <v>https://music.apple.com/us/album/house/1866696486</v>
+      </c>
+      <c r="L97" t="str">
+        <v>House - Connie Converse</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Cowboy Without a Clue</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>No Love Lost to Kindness</v>
+      </c>
+      <c r="G98" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Yumi Zouma</v>
+      </c>
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+      </c>
+      <c r="K98" t="str">
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G99" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H99" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K99" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Quien</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/quien/1870329662</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Quien - Single</v>
+      </c>
+      <c r="G100" t="str">
+        <v>4:19</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Daniela Darcourt</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/quien/1870329660</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Quien - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -588,13 +588,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>triston</v>
+        <v>tristón</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/triston/1872585947</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-30</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>triston - Single</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G6" t="str">
         <v>3:36</v>
@@ -618,10 +618,10 @@
         <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/triston/1872585761</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L6" t="str">
-        <v>triston - Fuerza Regida</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="7">

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -4160,13 +4160,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quien</v>
+        <v>Quién</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/quien/1870329662</v>
+        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-30</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Quien - Single</v>
+        <v>Quién - Single</v>
       </c>
       <c r="G100" t="str">
         <v>4:19</v>
@@ -4190,10 +4190,10 @@
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/quien/1870329660</v>
+        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
       <c r="L100" t="str">
-        <v>Quien - Daniela Darcourt</v>
+        <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -2506,7 +2506,7 @@
         <v>Frozen Lake - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:31</v>
+        <v>3:29</v>
       </c>
       <c r="H56" t="str">
         <v>VOILÀ</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -930,13 +930,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-30</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H15" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L15" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-30</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H16" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L16" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-30</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L17" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-30</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L18" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-30</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H19" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L19" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>professional heartbreaker</v>
+        <v>Free</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-30</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H20" t="str">
-        <v>Artemas</v>
+        <v>SLANDER</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L20" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-30</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H21" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L21" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-30</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G22" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H22" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L22" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-30</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H23" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L23" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-30</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H24" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L24" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-30</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G25" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H25" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L25" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-30</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H26" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L26" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-30</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H27" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L27" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-30</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H28" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L28" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-30</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G29" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H29" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L29" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-30</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L30" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-30</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H31" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L31" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-30</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H32" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L32" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-30</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G33" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H33" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L33" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-30</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G34" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H34" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L34" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-30</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G35" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H35" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L35" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-30</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G36" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H36" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L36" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-30</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G37" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H37" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L37" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-30</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G38" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H38" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L38" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-30</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G39" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H39" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L39" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-30</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G40" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H40" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L40" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-30</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G41" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H41" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L41" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Natural Disaster</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-30</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G42" t="str">
-        <v>3:02</v>
+        <v>1:59</v>
       </c>
       <c r="H42" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L42" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-30</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H43" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L43" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-30</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H44" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L44" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-30</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H45" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L45" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-30</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H46" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L46" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-30</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H47" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L47" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-30</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Too Late - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G48" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H48" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L48" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-30</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G49" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H49" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L49" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-30</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L50" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-30</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G51" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H51" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L51" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-30</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H52" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L52" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-30</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H53" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L53" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-30</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L54" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-30</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G55" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L55" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-30</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H56" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L56" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-30</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H57" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L57" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-30</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H58" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L58" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-30</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H59" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L59" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-30</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G60" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H60" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L60" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-30</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H61" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L61" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-30</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G62" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L62" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-30</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L63" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-30</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H64" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L64" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-30</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G65" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H65" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L65" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-30</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H66" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L66" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-30</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L67" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-30</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H68" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L68" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-30</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H69" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L69" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-30</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G70" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H70" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L70" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-30</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H71" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L71" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-30</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H72" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L72" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-30</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H73" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L73" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-30</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G74" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H74" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L74" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-30</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H75" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L75" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-30</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G76" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L76" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-30</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H77" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L77" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-30</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G78" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H78" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L78" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-30</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H79" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L79" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-30</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H80" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L80" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-30</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H81" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L81" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-30</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H82" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L82" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-30</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H83" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L83" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-30</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H84" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L84" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-30</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H85" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L85" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-30</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G86" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H86" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L86" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-30</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G87" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H87" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L87" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-30</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H88" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L88" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-30</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H89" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L89" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-30</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G90" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H90" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L90" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-30</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H91" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L91" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-30</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H92" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L92" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-30</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L93" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-30</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H94" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L94" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-30</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G95" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H95" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L95" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-30</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G96" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H96" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L96" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-30</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G97" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H97" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L97" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-30</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H98" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L98" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-30</v>
@@ -4137,68 +4137,106 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G99" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H99" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L99" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G100" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H100" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Quién</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>4:19</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -816,13 +816,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-30</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G12" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H12" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L12" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-30</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H13" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L13" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-30</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H14" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L14" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-30</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H15" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L15" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-30</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H16" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L16" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-30</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G17" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H17" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L17" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-30</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L18" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-30</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H19" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L19" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-30</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H20" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L20" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>professional heartbreaker</v>
+        <v>Free</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-30</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Artemas</v>
+        <v>SLANDER</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L21" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-30</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H22" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L22" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-30</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G23" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H23" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L23" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-30</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H24" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L24" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-30</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H25" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L25" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-30</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G26" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H26" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L26" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-30</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H27" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L27" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-30</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H28" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L28" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-30</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H29" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L29" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-30</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L30" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-30</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H31" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L31" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-30</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H32" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L32" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-30</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H33" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L33" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-30</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G34" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H34" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L34" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-30</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G35" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H35" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L35" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-30</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G36" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H36" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L36" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-30</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G37" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H37" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L37" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-30</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G38" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H38" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L38" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-30</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G39" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L39" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-30</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G40" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L40" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-30</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G41" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H41" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L41" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-30</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G42" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H42" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L42" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Natural Disaster</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-30</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G43" t="str">
-        <v>3:02</v>
+        <v>1:59</v>
       </c>
       <c r="H43" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L43" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-30</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H44" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L44" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-30</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H45" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L45" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-30</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H46" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L46" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-30</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H47" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L47" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-30</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H48" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L48" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-30</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Too Late - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G49" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H49" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L49" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-30</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G50" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H50" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L50" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-30</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H51" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L51" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-30</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G52" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H52" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L52" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-30</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H53" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L53" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-30</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H54" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L54" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-30</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L55" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-30</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G56" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H56" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L56" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-30</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H57" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L57" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-30</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H58" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L58" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-30</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H59" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L59" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-30</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H60" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L60" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-30</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G61" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H61" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L61" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-30</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H62" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L62" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-30</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G63" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H63" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L63" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-30</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H64" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L64" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-30</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L65" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-30</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G66" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L66" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-30</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H67" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L67" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-30</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H68" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L68" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-30</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H69" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L69" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-30</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H70" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L70" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-30</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G71" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H71" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L71" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-30</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H72" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L72" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-30</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H73" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L73" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-30</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H74" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L74" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-30</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G75" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H75" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L75" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-30</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H76" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L76" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-30</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G77" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L77" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-30</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H78" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L78" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-30</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G79" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H79" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L79" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-30</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H80" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L80" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-30</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H81" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L81" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-30</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H82" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L82" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-30</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L83" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-30</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H84" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L84" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-30</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H85" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L85" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-30</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H86" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L86" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-30</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G87" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H87" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L87" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-30</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G88" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H88" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L88" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-30</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H89" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L89" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-30</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H90" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L90" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-30</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G91" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H91" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L91" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-30</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H92" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L92" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-30</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H93" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L93" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-30</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H94" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L94" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-30</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H95" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L95" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-30</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G96" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H96" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L96" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-30</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G97" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H97" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L97" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-30</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G98" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H98" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L98" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-30</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H99" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L99" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-30</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H100" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L100" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G101" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H101" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>Quién</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>4:19</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2032,2249 +2032,2287 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Natural Disaster</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G44" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L44" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H45" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L45" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H46" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L46" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H47" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L47" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H48" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L48" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H49" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L49" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Too Late - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G50" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H50" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L50" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G51" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H51" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L51" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H52" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L52" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G53" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H53" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L53" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H54" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L54" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H55" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L55" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H56" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L56" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G57" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H57" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L57" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H58" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L58" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H59" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L59" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H60" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L60" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H61" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L61" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G62" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H62" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L62" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H63" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L63" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G64" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H64" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L64" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H65" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L65" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H66" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L66" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G67" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L67" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H68" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L68" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H69" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L69" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H70" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L70" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H71" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L71" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G72" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H72" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L72" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H73" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L73" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H74" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L74" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H75" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L75" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G76" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H76" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L76" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H77" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L77" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G78" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L78" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H79" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L79" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G80" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H80" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L80" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H81" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L81" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L82" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H83" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L83" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L84" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H85" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L85" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L86" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H87" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L87" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G88" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H88" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L88" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G89" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H89" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L89" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H90" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L90" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H91" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L91" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G92" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H92" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L92" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H93" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L93" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H94" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L94" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H95" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L95" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H96" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L96" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G97" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H97" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L97" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G98" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H98" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L98" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G99" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H99" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L99" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H100" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L100" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G101" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L101" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-31</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G102" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H102" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Quién</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D102" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
+      <c r="D103" t="str">
+        <v>2026-01-31</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G103" t="str">
         <v>4:19</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L103" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>